--- a/artfynd/A 58658-2023 artfynd.xlsx
+++ b/artfynd/A 58658-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58658-2023 artfynd.xlsx
+++ b/artfynd/A 58658-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2161,37 +2161,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66161858</v>
+        <v>66161864</v>
       </c>
       <c r="B15" t="n">
-        <v>4717</v>
+        <v>8240</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dialog hos rapportör</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>101937</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Aspborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Trypophloeus binodulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ratzeburg, 1837)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>670361.2214088396</v>
+        <v>670435.1180659346</v>
       </c>
       <c r="R15" t="n">
-        <v>6617033.017899103</v>
+        <v>6617180.111713775</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Grov gran</t>
+          <t>Asplåga med äldre angrepp. Finns inte så många lågor i området, men många aspar med aspticka, så mer ved kommer.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2275,123 +2275,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>66161864</v>
-      </c>
-      <c r="B16" t="n">
-        <v>8240</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>101937</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Aspborre</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Trypophloeus binodulus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Ratzeburg, 1837)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Trosta, Upl</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>670435.1180659346</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6617180.111713775</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Sigtuna</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Lunda</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2017-04-11</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2017-04-11</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Asplåga med äldre angrepp. Finns inte så många lågor i området, men många aspar med aspticka, så mer ved kommer.</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Hanna Nilsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Hanna Nilsson, Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
